--- a/public/exports-from-60/29189404.xlsx
+++ b/public/exports-from-60/29189404.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014098</t>
+          <t xml:space="preserve">200014104</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -26839,7 +26839,7 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t xml:space="preserve">311608657</t>
+          <t xml:space="preserve">311608660</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">

--- a/public/exports-from-60/29189404.xlsx
+++ b/public/exports-from-60/29189404.xlsx
@@ -19091,7 +19091,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agerskellet 13</t>
+          <t xml:space="preserve">Baunehøjparken 1B</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -19101,20 +19101,20 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">7568845</t>
+          <t xml:space="preserve">8907562</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J255">
-        <v>354</v>
+        <v>240</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023910</t>
+          <t xml:space="preserve">200023906</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjparken 1B</t>
+          <t xml:space="preserve">Frederiksborgvej 561</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19176,20 +19176,20 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">8907562</t>
+          <t xml:space="preserve">2178448</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J256">
-        <v>240</v>
+        <v>322</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023906</t>
+          <t xml:space="preserve">200023938</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19256,11 +19256,11 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J257">
-        <v>322</v>
+        <v>146</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
@@ -19316,40 +19316,40 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksborgvej 561</t>
+          <t xml:space="preserve">Grantoften 3</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178448</t>
+          <t xml:space="preserve">2217322</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J258">
-        <v>146</v>
+        <v>293</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023938</t>
+          <t xml:space="preserve">200024857</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-13</t>
+          <t xml:space="preserve">2019-12-01</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grantoften 3</t>
+          <t xml:space="preserve">Grantoften 5</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19406,11 +19406,11 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J259">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
@@ -19466,30 +19466,30 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grantoften 5</t>
+          <t xml:space="preserve">Hyrdehøj 62</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217322</t>
+          <t xml:space="preserve">9113193</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>392</v>
+        <v>722</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024857</t>
+          <t xml:space="preserve">200024858</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj 62</t>
+          <t xml:space="preserve">Kornvej 1</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">9113193</t>
+          <t xml:space="preserve">8550293</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -19560,11 +19560,11 @@
         </is>
       </c>
       <c r="J261">
-        <v>722</v>
+        <v>812</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024858</t>
+          <t xml:space="preserve">200024855</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kornvej 1</t>
+          <t xml:space="preserve">Dommervænget 30</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550293</t>
+          <t xml:space="preserve">5306255</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -19635,11 +19635,11 @@
         </is>
       </c>
       <c r="J262">
-        <v>812</v>
+        <v>1225</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024855</t>
+          <t xml:space="preserve">200024872</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-01</t>
+          <t xml:space="preserve">2019-12-02</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,17 +19691,17 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dommervænget 30</t>
+          <t xml:space="preserve">Bygaden 28</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306255</t>
+          <t xml:space="preserve">2178710</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -19710,11 +19710,11 @@
         </is>
       </c>
       <c r="J263">
-        <v>1225</v>
+        <v>263</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024872</t>
+          <t xml:space="preserve">200024953</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-02</t>
+          <t xml:space="preserve">2019-12-03</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19766,17 +19766,17 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 28</t>
+          <t xml:space="preserve">Gammel Darupvej 3</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178710</t>
+          <t xml:space="preserve">5307880</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -19785,11 +19785,11 @@
         </is>
       </c>
       <c r="J264">
-        <v>263</v>
+        <v>1383</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024953</t>
+          <t xml:space="preserve">200024956</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Darupvej 3</t>
+          <t xml:space="preserve">Lysalleen 33</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307880</t>
+          <t xml:space="preserve">8717244</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -19860,11 +19860,11 @@
         </is>
       </c>
       <c r="J265">
-        <v>1383</v>
+        <v>1298</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024956</t>
+          <t xml:space="preserve">200024948</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lysalleen 33</t>
+          <t xml:space="preserve">Eriksvej 40C</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19926,20 +19926,20 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">8717244</t>
+          <t xml:space="preserve">5308364</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J266">
-        <v>1298</v>
+        <v>852</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024948</t>
+          <t xml:space="preserve">200024993</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-03</t>
+          <t xml:space="preserve">2019-12-04</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 40C</t>
+          <t xml:space="preserve">Københavnsvej 106C</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20001,20 +20001,20 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308364</t>
+          <t xml:space="preserve">7896055</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J267">
-        <v>852</v>
+        <v>680</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024993</t>
+          <t xml:space="preserve">200024994</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 106C</t>
+          <t xml:space="preserve">Kamstrupsti 2</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -20076,30 +20076,30 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">7896055</t>
+          <t xml:space="preserve">5308151</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J268">
-        <v>680</v>
+        <v>400</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024994</t>
+          <t xml:space="preserve">200027969</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-04</t>
+          <t xml:space="preserve">2020-02-11</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamstrupsti 2</t>
+          <t xml:space="preserve">Svogerslev Hovedgade 70A</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -20151,30 +20151,30 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308151</t>
+          <t xml:space="preserve">8995659</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J269">
-        <v>400</v>
+        <v>995</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027969</t>
+          <t xml:space="preserve">200030999</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+          <t xml:space="preserve">BALSLEV</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-11</t>
+          <t xml:space="preserve">2020-05-03</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svogerslev Hovedgade 70A</t>
+          <t xml:space="preserve">Astersvej 9</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -20226,30 +20226,30 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995659</t>
+          <t xml:space="preserve">5308975</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J270">
-        <v>995</v>
+        <v>4292</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030999</t>
+          <t xml:space="preserve">200049549</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALSLEV</t>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-03</t>
+          <t xml:space="preserve">2021-05-26</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 9</t>
+          <t xml:space="preserve">Stændertorvet 1D</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -20301,7 +20301,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308975</t>
+          <t xml:space="preserve">5304086</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -20310,11 +20310,11 @@
         </is>
       </c>
       <c r="J271">
-        <v>4292</v>
+        <v>1906</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">200049549</t>
+          <t xml:space="preserve">200050785</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-05-26</t>
+          <t xml:space="preserve">2021-06-29</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stændertorvet 1D</t>
+          <t xml:space="preserve">Mosestykket 21</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -20376,7 +20376,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304086</t>
+          <t xml:space="preserve">2208892</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -20385,11 +20385,11 @@
         </is>
       </c>
       <c r="J272">
-        <v>1906</v>
+        <v>228</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050785</t>
+          <t xml:space="preserve">100235815</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-29</t>
+          <t xml:space="preserve">2021-08-03</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20456,15 +20456,15 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J273">
-        <v>228</v>
+        <v>770</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">100235815</t>
+          <t xml:space="preserve">200051688</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosestykket 21</t>
+          <t xml:space="preserve">Københavnsvej 266</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20526,30 +20526,30 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208892</t>
+          <t xml:space="preserve">5307061</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J274">
-        <v>770</v>
+        <v>573</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051688</t>
+          <t xml:space="preserve">200057196</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve">Forum r.i.</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-03</t>
+          <t xml:space="preserve">2022-02-06</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20606,11 +20606,11 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J275">
-        <v>573</v>
+        <v>137</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
@@ -20681,11 +20681,11 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J276">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
@@ -20756,11 +20756,11 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J277">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
@@ -20831,11 +20831,11 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J278">
-        <v>235</v>
+        <v>166</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J279">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 266</t>
+          <t xml:space="preserve">Københavnsvej 266B</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -20981,11 +20981,11 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J280">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 266B</t>
+          <t xml:space="preserve">Vestre Hedevej 10</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -21056,11 +21056,11 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J281">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J282">
@@ -21206,11 +21206,11 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J283">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Hedevej 10</t>
+          <t xml:space="preserve">Møllehusvej 13</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -21276,30 +21276,30 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307061</t>
+          <t xml:space="preserve">8135053</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J284">
-        <v>175</v>
+        <v>9546</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057196</t>
+          <t xml:space="preserve">200057529</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forum r.i.</t>
+          <t xml:space="preserve">TopDahl ApS</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-06</t>
+          <t xml:space="preserve">2022-02-20</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21341,7 +21341,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehusvej 13</t>
+          <t xml:space="preserve">Herregårdsvej 42</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">8135053</t>
+          <t xml:space="preserve">2172718</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -21360,11 +21360,11 @@
         </is>
       </c>
       <c r="J285">
-        <v>9546</v>
+        <v>1898</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057529</t>
+          <t xml:space="preserve">200057621</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-20</t>
+          <t xml:space="preserve">2022-02-23</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herregårdsvej 42</t>
+          <t xml:space="preserve">Ringstedgade 8</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -21426,30 +21426,30 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172718</t>
+          <t xml:space="preserve">5303896</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J286">
-        <v>1898</v>
+        <v>179</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057621</t>
+          <t xml:space="preserve">200057923</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">TopDahl ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-23</t>
+          <t xml:space="preserve">2022-03-08</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -21491,40 +21491,40 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedgade 8</t>
+          <t xml:space="preserve">Tranevej 7</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303896</t>
+          <t xml:space="preserve">7938930</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J287">
-        <v>179</v>
+        <v>638</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057923</t>
+          <t xml:space="preserve">200060567</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-03-08</t>
+          <t xml:space="preserve">2022-06-29</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranevej 7</t>
+          <t xml:space="preserve">Baunegårdsvej 80</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -21576,30 +21576,30 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">7938930</t>
+          <t xml:space="preserve">2179645</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J288">
-        <v>638</v>
+        <v>677</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">200060567</t>
+          <t xml:space="preserve">311052501</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-29</t>
+          <t xml:space="preserve">2024-05-06</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -21641,40 +21641,40 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 80</t>
+          <t xml:space="preserve">Højbakken 2</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179645</t>
+          <t xml:space="preserve">10229610</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J289">
-        <v>677</v>
+        <v>620</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311052501</t>
+          <t xml:space="preserve">311060924</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-06</t>
+          <t xml:space="preserve">2024-06-23</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -21731,11 +21731,11 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J290">
-        <v>620</v>
+        <v>1226</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højbakken 2</t>
+          <t xml:space="preserve">Højbakken 8</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -21806,11 +21806,11 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J291">
-        <v>1226</v>
+        <v>193</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -21866,40 +21866,40 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højbakken 8</t>
+          <t xml:space="preserve">Frederiksborgvej 561</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">10229610</t>
+          <t xml:space="preserve">2178448</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J292">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311060924</t>
+          <t xml:space="preserve">311062021</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-06-23</t>
+          <t xml:space="preserve">2024-06-27</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21941,40 +21941,40 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksborgvej 561</t>
+          <t xml:space="preserve">Baunehøjvej 5</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178448</t>
+          <t xml:space="preserve">2174626</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J293">
-        <v>216</v>
+        <v>287</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311062021</t>
+          <t xml:space="preserve">311082107</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-06-27</t>
+          <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -22016,7 +22016,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 5</t>
+          <t xml:space="preserve">Henrik Nielsens Vej 43</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -22026,7 +22026,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174626</t>
+          <t xml:space="preserve">5309424</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -22035,11 +22035,11 @@
         </is>
       </c>
       <c r="J294">
-        <v>287</v>
+        <v>2196</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082107</t>
+          <t xml:space="preserve">311082106</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Nielsens Vej 43</t>
+          <t xml:space="preserve">Himmelev Bygade 22C</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -22101,20 +22101,20 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">5309424</t>
+          <t xml:space="preserve">8995636</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J295">
-        <v>2196</v>
+        <v>426</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082106</t>
+          <t xml:space="preserve">311082104</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmelev Bygade 22C</t>
+          <t xml:space="preserve">Bindesbøll Alle 32</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -22176,30 +22176,30 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995636</t>
+          <t xml:space="preserve">5312015</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">129</t>
         </is>
       </c>
       <c r="J296">
-        <v>426</v>
+        <v>214</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082104</t>
+          <t xml:space="preserve">311083529</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-06</t>
+          <t xml:space="preserve">2024-11-14</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -22241,7 +22241,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bindesbøll Alle 32</t>
+          <t xml:space="preserve">Bistruphøj 2</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -22251,25 +22251,25 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312015</t>
+          <t xml:space="preserve">5312115</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">129</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J297">
-        <v>214</v>
+        <v>1048</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311083529</t>
+          <t xml:space="preserve">311083539</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistruphøj 2</t>
+          <t xml:space="preserve">Bistrupvænge 16</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -22326,25 +22326,25 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312115</t>
+          <t xml:space="preserve">5312015</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="J298">
-        <v>1048</v>
+        <v>927</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311083539</t>
+          <t xml:space="preserve">311083529</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvænge 16</t>
+          <t xml:space="preserve">Lindegårdsparken 1</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -22406,11 +22406,11 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">139</t>
         </is>
       </c>
       <c r="J299">
-        <v>927</v>
+        <v>20718</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsparken 1</t>
+          <t xml:space="preserve">Parcelgårdsvej 4</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -22476,25 +22476,25 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312015</t>
+          <t xml:space="preserve">5312129</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">139</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J300">
-        <v>20718</v>
+        <v>160</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311083529</t>
+          <t xml:space="preserve">311083546</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcelgårdsvej 4</t>
+          <t xml:space="preserve">Parcelgårdsvej 6</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312129</t>
+          <t xml:space="preserve">5312130</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -22564,7 +22564,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311083546</t>
+          <t xml:space="preserve">311083544</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcelgårdsvej 6</t>
+          <t xml:space="preserve">Ollerupvej 10</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312130</t>
+          <t xml:space="preserve">2173593</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -22635,11 +22635,11 @@
         </is>
       </c>
       <c r="J302">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311083544</t>
+          <t xml:space="preserve">311088229</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-14</t>
+          <t xml:space="preserve">2024-12-16</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollerupvej 10</t>
+          <t xml:space="preserve">Dronning Sofies Vej 10</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -22701,7 +22701,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173593</t>
+          <t xml:space="preserve">5310451</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -22710,11 +22710,11 @@
         </is>
       </c>
       <c r="J303">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311088229</t>
+          <t xml:space="preserve">311091394</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -22724,7 +22724,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-12-16</t>
+          <t xml:space="preserve">2025-01-16</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -22766,7 +22766,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Sofies Vej 10</t>
+          <t xml:space="preserve">Rønøs Alle 38</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -22776,20 +22776,20 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">5310451</t>
+          <t xml:space="preserve">5308584</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J304">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311091394</t>
+          <t xml:space="preserve">311091392</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -22841,7 +22841,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønøs Alle 38</t>
+          <t xml:space="preserve">Nygade 13</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -22851,20 +22851,20 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308584</t>
+          <t xml:space="preserve">5312309</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J305">
-        <v>152</v>
+        <v>568</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311091392</t>
+          <t xml:space="preserve">311096313</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-16</t>
+          <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -22916,7 +22916,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 13</t>
+          <t xml:space="preserve">Nygade 14</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -22931,7 +22931,7 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J306">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 14</t>
+          <t xml:space="preserve">Nygade 18</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -23006,7 +23006,7 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J307">
@@ -23066,30 +23066,30 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 18</t>
+          <t xml:space="preserve">Rosenhaven 1</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312309</t>
+          <t xml:space="preserve">2177192</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J308">
-        <v>568</v>
+        <v>202</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096313</t>
+          <t xml:space="preserve">311098182</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -23099,7 +23099,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-19</t>
+          <t xml:space="preserve">2025-03-02</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -23141,7 +23141,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenhaven 1</t>
+          <t xml:space="preserve">Rosenhaven 13</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -23156,11 +23156,11 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J309">
-        <v>202</v>
+        <v>268</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenhaven 13</t>
+          <t xml:space="preserve">Rosenhaven 2</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -23231,11 +23231,11 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J310">
-        <v>268</v>
+        <v>202</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenhaven 2</t>
+          <t xml:space="preserve">Rosenhaven 7</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J311">
@@ -23366,22 +23366,22 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenhaven 7</t>
+          <t xml:space="preserve">Bryggerbakken 1</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177192</t>
+          <t xml:space="preserve">8841780</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J312">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098182</t>
+          <t xml:space="preserve">311098897</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -23399,7 +23399,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-02</t>
+          <t xml:space="preserve">2025-03-05</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggerbakken 1</t>
+          <t xml:space="preserve">Bryggerbakken 4</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -23456,7 +23456,7 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J313">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggerbakken 4</t>
+          <t xml:space="preserve">Havnevej 38</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -23526,20 +23526,20 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">8841780</t>
+          <t xml:space="preserve">5304807, 100884599</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J314">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098897</t>
+          <t xml:space="preserve">311100067</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
@@ -23549,7 +23549,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-05</t>
+          <t xml:space="preserve">2025-03-11</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -23591,7 +23591,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 38</t>
+          <t xml:space="preserve">Helligkorsvej 2</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304807, 100884599</t>
+          <t xml:space="preserve">5309444</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -23610,11 +23610,11 @@
         </is>
       </c>
       <c r="J315">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311100067</t>
+          <t xml:space="preserve">311100272</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -23624,7 +23624,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-11</t>
+          <t xml:space="preserve">2025-03-12</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -23681,11 +23681,11 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J316">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
@@ -23741,30 +23741,30 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helligkorsvej 2</t>
+          <t xml:space="preserve">Toftevej 7</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">5309444</t>
+          <t xml:space="preserve">2213788</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J317">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311100272</t>
+          <t xml:space="preserve">311100395</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -23816,30 +23816,30 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftevej 7</t>
+          <t xml:space="preserve">Strandvejen 18</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213788</t>
+          <t xml:space="preserve">2174669</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J318">
-        <v>197</v>
+        <v>401</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311100395</t>
+          <t xml:space="preserve">311101306</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -23849,7 +23849,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-12</t>
+          <t xml:space="preserve">2025-03-17</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -23891,7 +23891,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 18</t>
+          <t xml:space="preserve">Klosterengen 150</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174669</t>
+          <t xml:space="preserve">2172798</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -23910,11 +23910,11 @@
         </is>
       </c>
       <c r="J319">
-        <v>401</v>
+        <v>67</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311101306</t>
+          <t xml:space="preserve">311101901</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-17</t>
+          <t xml:space="preserve">2025-03-19</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klosterengen 150</t>
+          <t xml:space="preserve">Havnevej 40</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172798</t>
+          <t xml:space="preserve">5304808, 100884600</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -23985,11 +23985,11 @@
         </is>
       </c>
       <c r="J320">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311101901</t>
+          <t xml:space="preserve">311102141</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-19</t>
+          <t xml:space="preserve">2025-03-20</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 40</t>
+          <t xml:space="preserve">Sankt Ols Stræde 5</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304808, 100884600</t>
+          <t xml:space="preserve">5303417</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -24060,11 +24060,11 @@
         </is>
       </c>
       <c r="J321">
-        <v>205</v>
+        <v>482</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311102141</t>
+          <t xml:space="preserve">311109494</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -24074,7 +24074,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-20</t>
+          <t xml:space="preserve">2025-04-28</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Ols Stræde 5</t>
+          <t xml:space="preserve">Strandgade 2</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -24126,20 +24126,20 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303417</t>
+          <t xml:space="preserve">5312664, 100884612</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J322">
-        <v>482</v>
+        <v>345</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311109494</t>
+          <t xml:space="preserve">311110647</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-28</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgade 2</t>
+          <t xml:space="preserve">Lammegade 26</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -24201,20 +24201,20 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312664, 100884612</t>
+          <t xml:space="preserve">5303695</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J323">
-        <v>345</v>
+        <v>667</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110647</t>
+          <t xml:space="preserve">311112925</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -24266,7 +24266,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 26</t>
+          <t xml:space="preserve">Lammegade 28</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -24281,7 +24281,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J324">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 28</t>
+          <t xml:space="preserve">Lammegade 30</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -24356,11 +24356,11 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J325">
-        <v>667</v>
+        <v>496</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 30</t>
+          <t xml:space="preserve">Lammegade 36</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -24431,11 +24431,11 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J326">
-        <v>496</v>
+        <v>624</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 36</t>
+          <t xml:space="preserve">Vestergade 6A</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -24501,20 +24501,20 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303695</t>
+          <t xml:space="preserve">5312565</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J327">
-        <v>624</v>
+        <v>3282</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311112925</t>
+          <t xml:space="preserve">311115034</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -24524,7 +24524,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-26</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -24566,7 +24566,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 6A</t>
+          <t xml:space="preserve">Lyngbakken 1</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -24576,7 +24576,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312565</t>
+          <t xml:space="preserve">7175316</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -24585,11 +24585,11 @@
         </is>
       </c>
       <c r="J328">
-        <v>3282</v>
+        <v>362</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311115034</t>
+          <t xml:space="preserve">311118205</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-26</t>
+          <t xml:space="preserve">2025-06-10</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -24641,7 +24641,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngbakken 1</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 6</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -24651,7 +24651,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">7175316</t>
+          <t xml:space="preserve">2170239</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -24660,11 +24660,11 @@
         </is>
       </c>
       <c r="J329">
-        <v>362</v>
+        <v>120</v>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311118205</t>
+          <t xml:space="preserve">311118198</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -24716,7 +24716,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 6</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 8</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -24726,7 +24726,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170239</t>
+          <t xml:space="preserve">2170234</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -24735,11 +24735,11 @@
         </is>
       </c>
       <c r="J330">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311118198</t>
+          <t xml:space="preserve">311118200</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24791,7 +24791,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 8</t>
+          <t xml:space="preserve">Navervej 16</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -24801,7 +24801,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170234</t>
+          <t xml:space="preserve">2209531</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -24810,11 +24810,11 @@
         </is>
       </c>
       <c r="J331">
-        <v>176</v>
+        <v>1432</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311118200</t>
+          <t xml:space="preserve">311124782</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -24824,7 +24824,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-10</t>
+          <t xml:space="preserve">2025-07-13</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -24881,11 +24881,11 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J332">
-        <v>1432</v>
+        <v>979</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Navervej 16</t>
+          <t xml:space="preserve">Margrethehåbsvej 112</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -24951,20 +24951,20 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209531</t>
+          <t xml:space="preserve">7242878</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J333">
-        <v>979</v>
+        <v>116</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t xml:space="preserve">311124782</t>
+          <t xml:space="preserve">311127122</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -24974,7 +24974,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-13</t>
+          <t xml:space="preserve">2025-07-31</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -25016,7 +25016,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethehåbsvej 112</t>
+          <t xml:space="preserve">Vesterdal 3</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">7242878</t>
+          <t xml:space="preserve">5312033</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -25035,11 +25035,11 @@
         </is>
       </c>
       <c r="J334">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">311127122</t>
+          <t xml:space="preserve">311128107</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -25049,7 +25049,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-31</t>
+          <t xml:space="preserve">2025-08-07</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -25091,7 +25091,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterdal 3</t>
+          <t xml:space="preserve">Rabalderstræde 16</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -25101,30 +25101,30 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312033</t>
+          <t xml:space="preserve">719145, 100067704</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J335">
-        <v>98</v>
+        <v>3529</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">311128107</t>
+          <t xml:space="preserve">311137096</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-07</t>
+          <t xml:space="preserve">2025-09-28</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -25166,7 +25166,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rabalderstræde 16</t>
+          <t xml:space="preserve">Jernbanegade 21A</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -25176,30 +25176,30 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">719145, 100067704</t>
+          <t xml:space="preserve">8995769</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J336">
-        <v>3529</v>
+        <v>1236</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">311137096</t>
+          <t xml:space="preserve">311162791</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">Boligeftersyn P/S</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-28</t>
+          <t xml:space="preserve">2026-03-07</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -25241,7 +25241,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 21A</t>
+          <t xml:space="preserve">Rabalderstræde 34</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -25251,40 +25251,40 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995769</t>
+          <t xml:space="preserve">719163, 5308146</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="J337">
-        <v>1236</v>
+        <v>110</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t xml:space="preserve">311162791</t>
+          <t xml:space="preserve">311217288</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligeftersyn P/S</t>
+          <t xml:space="preserve">BF Byggeservice ApS</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-07</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -25316,7 +25316,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rabalderstræde 34</t>
+          <t xml:space="preserve">Vestre Hedevej 32</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -25326,30 +25326,30 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">719163, 5308146</t>
+          <t xml:space="preserve">719290, 100013803</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J338">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217288</t>
+          <t xml:space="preserve">311241595</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">BF Byggeservice ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -25406,11 +25406,11 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J339">
-        <v>96</v>
+        <v>276</v>
       </c>
       <c r="K339" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Hedevej 32</t>
+          <t xml:space="preserve">Astersvej 25</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -25476,30 +25476,30 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">719290, 100013803</t>
+          <t xml:space="preserve">5308666</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J340">
-        <v>276</v>
+        <v>238</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241595</t>
+          <t xml:space="preserve">311292852</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">dansk drift center ApS</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2028-01-16</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -25541,7 +25541,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 25</t>
+          <t xml:space="preserve">Basgangen 20</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -25551,30 +25551,30 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308666</t>
+          <t xml:space="preserve">719167, 100093183</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="J341">
-        <v>238</v>
+        <v>2980</v>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311292852</t>
+          <t xml:space="preserve">311351867</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">dansk drift center ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-16</t>
+          <t xml:space="preserve">2028-12-17</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basgangen 20</t>
+          <t xml:space="preserve">Hyrdehøj Stræde 2</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -25626,30 +25626,30 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">719167, 100093183</t>
+          <t xml:space="preserve">100122346</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J342">
-        <v>2980</v>
+        <v>9549</v>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">311351867</t>
+          <t xml:space="preserve">311522399</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-17</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -25691,40 +25691,40 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj Stræde 2</t>
+          <t xml:space="preserve">Søndergade 11</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">100122346</t>
+          <t xml:space="preserve">7855029</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J343">
-        <v>9549</v>
+        <v>1530</v>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522399</t>
+          <t xml:space="preserve">311552201</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-09-30</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -25766,40 +25766,40 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 11</t>
+          <t xml:space="preserve">Sandhøjsvej 4</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">7855029</t>
+          <t xml:space="preserve">1304635</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J344">
-        <v>1530</v>
+        <v>599</v>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552201</t>
+          <t xml:space="preserve">311569226</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-30</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandhøjsvej 4</t>
+          <t xml:space="preserve">Ramsømaglevej 17B</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304635</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -25860,11 +25860,11 @@
         </is>
       </c>
       <c r="J345">
-        <v>599</v>
+        <v>1459</v>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569226</t>
+          <t xml:space="preserve">311570325</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -25874,7 +25874,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -25916,7 +25916,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17B</t>
+          <t xml:space="preserve">Ramsømaglevej 17D</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -25931,15 +25931,15 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J346">
-        <v>1459</v>
+        <v>355</v>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570325</t>
+          <t xml:space="preserve">311570327</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -25991,40 +25991,40 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17D</t>
+          <t xml:space="preserve">Penselstrøget 44</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">719164, 5308146</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="J347">
-        <v>355</v>
+        <v>150</v>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570327</t>
+          <t xml:space="preserve">311576620</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">EnergiFocus ApS</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-03</t>
+          <t xml:space="preserve">2032-02-03</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penselstrøget 44</t>
+          <t xml:space="preserve">Ejboparken 6</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -26076,30 +26076,30 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">719164, 5308146</t>
+          <t xml:space="preserve">7174735</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J348">
-        <v>150</v>
+        <v>435</v>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">311576620</t>
+          <t xml:space="preserve">311586207</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiFocus ApS</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-03</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -26141,7 +26141,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 6</t>
+          <t xml:space="preserve">Ejboparken 6B</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -26156,11 +26156,11 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J349">
-        <v>435</v>
+        <v>517</v>
       </c>
       <c r="K349" t="inlineStr">
         <is>
@@ -26231,11 +26231,11 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J350">
-        <v>517</v>
+        <v>258</v>
       </c>
       <c r="K350" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 6B</t>
+          <t xml:space="preserve">Ejboparken 8A</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -26306,11 +26306,11 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J351">
-        <v>258</v>
+        <v>477</v>
       </c>
       <c r="K351" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 8A</t>
+          <t xml:space="preserve">Ejboparken 8B</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -26381,11 +26381,11 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J352">
-        <v>477</v>
+        <v>229</v>
       </c>
       <c r="K352" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 8B</t>
+          <t xml:space="preserve">Hørhusene 61</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -26451,20 +26451,20 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">7174735</t>
+          <t xml:space="preserve">5312139</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J353">
-        <v>229</v>
+        <v>826</v>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586207</t>
+          <t xml:space="preserve">311595512</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -26531,11 +26531,11 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J354">
-        <v>826</v>
+        <v>176</v>
       </c>
       <c r="K354" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørhusene 61</t>
+          <t xml:space="preserve">Københavnsvej 266C</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -26601,30 +26601,30 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312139</t>
+          <t xml:space="preserve">5307061</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J355">
-        <v>176</v>
+        <v>322</v>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t xml:space="preserve">311595512</t>
+          <t xml:space="preserve">311587049</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-22</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -26666,40 +26666,40 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 266C</t>
+          <t xml:space="preserve">Bueager 8</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307061</t>
+          <t xml:space="preserve">2211135</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J356">
-        <v>322</v>
+        <v>469</v>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587049</t>
+          <t xml:space="preserve">311608657</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Botjek Energi og bæredygtighed</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-22</t>
+          <t xml:space="preserve">2032-06-17</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -26741,7 +26741,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 8</t>
+          <t xml:space="preserve">Bueager 2</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -26756,15 +26756,15 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J357">
-        <v>469</v>
+        <v>4564</v>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t xml:space="preserve">311608657</t>
+          <t xml:space="preserve">311610029</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -26774,7 +26774,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-17</t>
+          <t xml:space="preserve">2032-06-23</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -26831,11 +26831,11 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J358">
-        <v>4564</v>
+        <v>92</v>
       </c>
       <c r="K358" t="inlineStr">
         <is>
@@ -26906,11 +26906,11 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J359">
-        <v>92</v>
+        <v>2127</v>
       </c>
       <c r="K359" t="inlineStr">
         <is>
@@ -26981,11 +26981,11 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J360">
-        <v>2127</v>
+        <v>847</v>
       </c>
       <c r="K360" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 2</t>
+          <t xml:space="preserve">Bueager 6</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -27056,15 +27056,15 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J361">
-        <v>847</v>
+        <v>1898</v>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610029</t>
+          <t xml:space="preserve">311610041</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -27116,40 +27116,40 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 6</t>
+          <t xml:space="preserve">Køgevej 106</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211135</t>
+          <t xml:space="preserve">5308417</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J362">
-        <v>1898</v>
+        <v>1620</v>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610041</t>
+          <t xml:space="preserve">311626283</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Energi og bæredygtighed</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-23</t>
+          <t xml:space="preserve">2032-09-08</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -27191,40 +27191,40 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Køgevej 106</t>
+          <t xml:space="preserve">Snoldelev Bygade 21A</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308417</t>
+          <t xml:space="preserve">2202050</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J363">
-        <v>1620</v>
+        <v>157</v>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626283</t>
+          <t xml:space="preserve">311633114</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-08</t>
+          <t xml:space="preserve">2032-10-04</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snoldelev Bygade 21A</t>
+          <t xml:space="preserve">Snoldelev Bygade 21B</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -27281,15 +27281,15 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J364">
-        <v>157</v>
+        <v>438</v>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633114</t>
+          <t xml:space="preserve">311633105</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -27341,17 +27341,17 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snoldelev Bygade 21B</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 65</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">2202050</t>
+          <t xml:space="preserve">2170541</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -27360,11 +27360,11 @@
         </is>
       </c>
       <c r="J365">
-        <v>438</v>
+        <v>1257</v>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633105</t>
+          <t xml:space="preserve">311633102</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -27416,7 +27416,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 65</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 67</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -27426,7 +27426,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170541</t>
+          <t xml:space="preserve">8016122</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -27435,21 +27435,21 @@
         </is>
       </c>
       <c r="J366">
-        <v>1257</v>
+        <v>2104</v>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633102</t>
+          <t xml:space="preserve">311645050</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-04</t>
+          <t xml:space="preserve">2032-11-08</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -27491,7 +27491,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 67</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 67B</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -27506,11 +27506,11 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J367">
-        <v>2104</v>
+        <v>434</v>
       </c>
       <c r="K367" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 67B</t>
+          <t xml:space="preserve">Vindeboder 15</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -27576,30 +27576,30 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t xml:space="preserve">8016122</t>
+          <t xml:space="preserve">8934798, 100153741</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="J368">
-        <v>434</v>
+        <v>225</v>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645050</t>
+          <t xml:space="preserve">311642567</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-08</t>
+          <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -27641,7 +27641,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeboder 15</t>
+          <t xml:space="preserve">Gundsølillevej 2</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -27651,30 +27651,30 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">8934798, 100153741</t>
+          <t xml:space="preserve">2167605</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J369">
-        <v>225</v>
+        <v>979</v>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642567</t>
+          <t xml:space="preserve">311643576</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-15</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -27716,7 +27716,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gundsølillevej 2</t>
+          <t xml:space="preserve">Gundsølillevej 6</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -27731,15 +27731,15 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J370">
-        <v>979</v>
+        <v>4101</v>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643576</t>
+          <t xml:space="preserve">311643577</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gundsølillevej 6</t>
+          <t xml:space="preserve">Sognevej 50</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -27801,20 +27801,20 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167605</t>
+          <t xml:space="preserve">2172270</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J371">
-        <v>4101</v>
+        <v>3519</v>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643577</t>
+          <t xml:space="preserve">311644570</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -27824,7 +27824,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-23</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -27866,17 +27866,17 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognevej 50</t>
+          <t xml:space="preserve">Planetvej 30</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172270</t>
+          <t xml:space="preserve">8907547</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -27885,21 +27885,21 @@
         </is>
       </c>
       <c r="J372">
-        <v>3519</v>
+        <v>897</v>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644570</t>
+          <t xml:space="preserve">311644810</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">BOTJEK A/S</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-23</t>
+          <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -27956,11 +27956,11 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J373">
-        <v>897</v>
+        <v>398</v>
       </c>
       <c r="K373" t="inlineStr">
         <is>
@@ -28031,11 +28031,11 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J374">
-        <v>398</v>
+        <v>1311</v>
       </c>
       <c r="K374" t="inlineStr">
         <is>
@@ -28106,11 +28106,11 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J375">
-        <v>1311</v>
+        <v>924</v>
       </c>
       <c r="K375" t="inlineStr">
         <is>
@@ -28181,11 +28181,11 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J376">
-        <v>924</v>
+        <v>487</v>
       </c>
       <c r="K376" t="inlineStr">
         <is>
@@ -28256,11 +28256,11 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J377">
-        <v>487</v>
+        <v>256</v>
       </c>
       <c r="K377" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J378">
@@ -28406,11 +28406,11 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J379">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="K379" t="inlineStr">
         <is>
@@ -28481,11 +28481,11 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J380">
-        <v>239</v>
+        <v>897</v>
       </c>
       <c r="K380" t="inlineStr">
         <is>
@@ -28556,11 +28556,11 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J381">
-        <v>897</v>
+        <v>983</v>
       </c>
       <c r="K381" t="inlineStr">
         <is>
@@ -28631,11 +28631,11 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J382">
-        <v>983</v>
+        <v>552</v>
       </c>
       <c r="K382" t="inlineStr">
         <is>
@@ -28706,11 +28706,11 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J383">
-        <v>552</v>
+        <v>897</v>
       </c>
       <c r="K383" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J384">
@@ -28856,11 +28856,11 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J385">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="K385" t="inlineStr">
         <is>
@@ -28931,11 +28931,11 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J386">
-        <v>898</v>
+        <v>280</v>
       </c>
       <c r="K386" t="inlineStr">
         <is>
@@ -29006,11 +29006,11 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J387">
-        <v>280</v>
+        <v>900</v>
       </c>
       <c r="K387" t="inlineStr">
         <is>
@@ -29081,11 +29081,11 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J388">
-        <v>900</v>
+        <v>789</v>
       </c>
       <c r="K388" t="inlineStr">
         <is>
@@ -29141,40 +29141,40 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planetvej 30</t>
+          <t xml:space="preserve">H H Kochs Vej 4</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t xml:space="preserve">8907547</t>
+          <t xml:space="preserve">2173007</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J389">
-        <v>789</v>
+        <v>7796</v>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644810</t>
+          <t xml:space="preserve">311645058</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTJEK A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-24</t>
+          <t xml:space="preserve">2032-11-25</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -29216,7 +29216,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t xml:space="preserve">H H Kochs Vej 4</t>
+          <t xml:space="preserve">Skolevej 3</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -29226,7 +29226,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173007</t>
+          <t xml:space="preserve">2180519</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -29235,16 +29235,16 @@
         </is>
       </c>
       <c r="J390">
-        <v>7796</v>
+        <v>1448</v>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645058</t>
+          <t xml:space="preserve">311644999</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -29306,11 +29306,11 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J391">
-        <v>1448</v>
+        <v>112</v>
       </c>
       <c r="K391" t="inlineStr">
         <is>
@@ -29381,11 +29381,11 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J392">
-        <v>112</v>
+        <v>413</v>
       </c>
       <c r="K392" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 3</t>
+          <t xml:space="preserve">Lindelunden 1</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -29451,7 +29451,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180519</t>
+          <t xml:space="preserve">5306821</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -29460,21 +29460,21 @@
         </is>
       </c>
       <c r="J393">
-        <v>413</v>
+        <v>5829</v>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644999</t>
+          <t xml:space="preserve">311645727</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-25</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindelunden 1</t>
+          <t xml:space="preserve">Trekroner Centervej 41</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -29531,11 +29531,11 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J394">
-        <v>5829</v>
+        <v>12072</v>
       </c>
       <c r="K394" t="inlineStr">
         <is>
@@ -29591,17 +29591,17 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Centervej 41</t>
+          <t xml:space="preserve">Ramsømaglevej 19</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306821</t>
+          <t xml:space="preserve">2213437</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -29610,11 +29610,11 @@
         </is>
       </c>
       <c r="J395">
-        <v>12072</v>
+        <v>2744</v>
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645727</t>
+          <t xml:space="preserve">311646168</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -29681,15 +29681,15 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J396">
-        <v>2744</v>
+        <v>1287</v>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646168</t>
+          <t xml:space="preserve">311646167</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
@@ -29741,30 +29741,30 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 19</t>
+          <t xml:space="preserve">Gammel Vindingevej 10</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213437</t>
+          <t xml:space="preserve">2209330</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J397">
-        <v>1287</v>
+        <v>5956</v>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646167</t>
+          <t xml:space="preserve">311646682</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
@@ -29774,7 +29774,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-30</t>
+          <t xml:space="preserve">2032-12-02</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -29831,15 +29831,15 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J398">
-        <v>5956</v>
+        <v>246</v>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646682</t>
+          <t xml:space="preserve">311646684</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -29906,15 +29906,15 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J399">
-        <v>246</v>
+        <v>447</v>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646684</t>
+          <t xml:space="preserve">311646683</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
@@ -29966,7 +29966,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Vindingevej 10</t>
+          <t xml:space="preserve">Margrethekær 2</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -29976,20 +29976,20 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209330</t>
+          <t xml:space="preserve">9700889</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J400">
-        <v>447</v>
+        <v>2442</v>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646683</t>
+          <t xml:space="preserve">311647649</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
@@ -29999,7 +29999,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-02</t>
+          <t xml:space="preserve">2032-12-07</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -30041,7 +30041,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 2</t>
+          <t xml:space="preserve">Margrethekær 10</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
@@ -30056,15 +30056,15 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J401">
-        <v>2442</v>
+        <v>1500</v>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647649</t>
+          <t xml:space="preserve">311647742</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -30074,7 +30074,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-07</t>
+          <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -30116,7 +30116,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 10</t>
+          <t xml:space="preserve">Margrethekær 12</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -30131,11 +30131,11 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J402">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="K402" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 12</t>
+          <t xml:space="preserve">Margrethekær 4</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
@@ -30206,11 +30206,11 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J403">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="K403" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 4</t>
+          <t xml:space="preserve">Margrethekær 6</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -30281,11 +30281,11 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J404">
-        <v>1514</v>
+        <v>1500</v>
       </c>
       <c r="K404" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 6</t>
+          <t xml:space="preserve">Margrethekær 8</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -30356,11 +30356,11 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J405">
-        <v>1500</v>
+        <v>1577</v>
       </c>
       <c r="K405" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 8</t>
+          <t xml:space="preserve">Hyrdehøj 3</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -30426,30 +30426,30 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700889</t>
+          <t xml:space="preserve">7713101</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J406">
-        <v>1577</v>
+        <v>11744</v>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647742</t>
+          <t xml:space="preserve">311649946</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-08</t>
+          <t xml:space="preserve">2032-12-17</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -30506,15 +30506,15 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J407">
-        <v>11744</v>
+        <v>1185</v>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649946</t>
+          <t xml:space="preserve">311649970</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -30524,7 +30524,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-17</t>
+          <t xml:space="preserve">2032-12-18</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -30566,7 +30566,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj 3</t>
+          <t xml:space="preserve">Møllehusvej 118</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
@@ -30576,30 +30576,30 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t xml:space="preserve">7713101</t>
+          <t xml:space="preserve">258624, 258625</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J408">
-        <v>1185</v>
+        <v>4232</v>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649970</t>
+          <t xml:space="preserve">311650857</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-18</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -30641,17 +30641,17 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehusvej 118</t>
+          <t xml:space="preserve">Kirkebjergvej 2</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t xml:space="preserve">258624, 258625</t>
+          <t xml:space="preserve">2177192</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -30660,11 +30660,11 @@
         </is>
       </c>
       <c r="J409">
-        <v>4232</v>
+        <v>1786</v>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650857</t>
+          <t xml:space="preserve">311652564</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -30716,7 +30716,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 2</t>
+          <t xml:space="preserve">Kirkebjergvej 4</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
@@ -30731,15 +30731,15 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J410">
-        <v>1786</v>
+        <v>1585</v>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652564</t>
+          <t xml:space="preserve">311652563</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -30791,7 +30791,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 4</t>
+          <t xml:space="preserve">Kirkebjergvej 6</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
@@ -30806,15 +30806,15 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J411">
-        <v>1585</v>
+        <v>2239</v>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652563</t>
+          <t xml:space="preserve">311652567</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 6</t>
+          <t xml:space="preserve">Kirkebjergvej 8</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
@@ -30881,15 +30881,15 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J412">
-        <v>2239</v>
+        <v>610</v>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652567</t>
+          <t xml:space="preserve">311652565</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -30941,40 +30941,40 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 8</t>
+          <t xml:space="preserve">Ørstedvej 63B</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177192</t>
+          <t xml:space="preserve">2217238</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J413">
-        <v>610</v>
+        <v>8368</v>
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652565</t>
+          <t xml:space="preserve">311652748</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-05</t>
+          <t xml:space="preserve">2033-01-06</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -31016,40 +31016,40 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 63B</t>
+          <t xml:space="preserve">Ramsømaglevej 17C</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217238</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J414">
-        <v>8368</v>
+        <v>1815</v>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652748</t>
+          <t xml:space="preserve">311652906</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-06</t>
+          <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -31106,11 +31106,11 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J415">
-        <v>1815</v>
+        <v>2850</v>
       </c>
       <c r="K415" t="inlineStr">
         <is>
@@ -31181,11 +31181,11 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J416">
-        <v>2850</v>
+        <v>1908</v>
       </c>
       <c r="K416" t="inlineStr">
         <is>
@@ -31241,40 +31241,40 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17C</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 14</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">5304953</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J417">
-        <v>1908</v>
+        <v>6173</v>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652906</t>
+          <t xml:space="preserve">311656342</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-09</t>
+          <t xml:space="preserve">2033-01-20</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -31316,7 +31316,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 14</t>
+          <t xml:space="preserve">Gormsvej 7</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
@@ -31326,20 +31326,20 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304953</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J418">
-        <v>6173</v>
+        <v>203</v>
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656342</t>
+          <t xml:space="preserve">311655571</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
@@ -31349,7 +31349,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-20</t>
+          <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -31391,7 +31391,7 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 7</t>
+          <t xml:space="preserve">Københavnsvej 34</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
@@ -31401,25 +31401,25 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">5311321</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J419">
-        <v>203</v>
+        <v>9899</v>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655571</t>
+          <t xml:space="preserve">311655694</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
@@ -31481,11 +31481,11 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J420">
-        <v>9899</v>
+        <v>158</v>
       </c>
       <c r="K420" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 34</t>
+          <t xml:space="preserve">Rådhusbuen 1</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
@@ -31551,25 +31551,25 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t xml:space="preserve">5311321</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J421">
-        <v>158</v>
+        <v>9084</v>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655694</t>
+          <t xml:space="preserve">311655558</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -31616,7 +31616,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusbuen 1</t>
+          <t xml:space="preserve">Bymarken 37</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
@@ -31626,20 +31626,20 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">5306248</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J422">
-        <v>9084</v>
+        <v>8569</v>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655558</t>
+          <t xml:space="preserve">311656548</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
@@ -31649,7 +31649,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-23</t>
+          <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -31691,7 +31691,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bymarken 37</t>
+          <t xml:space="preserve">Gormsvej 7</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
@@ -31701,20 +31701,20 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306248</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J423">
-        <v>8569</v>
+        <v>160</v>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656548</t>
+          <t xml:space="preserve">311656779</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-27</t>
+          <t xml:space="preserve">2033-01-30</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -31766,7 +31766,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 7</t>
+          <t xml:space="preserve">Gormsvej 9</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
@@ -31781,15 +31781,15 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J424">
-        <v>160</v>
+        <v>214</v>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656779</t>
+          <t xml:space="preserve">311656783</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
@@ -31841,7 +31841,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 9</t>
+          <t xml:space="preserve">Gormsvej 9B</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
@@ -31856,15 +31856,15 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J425">
-        <v>214</v>
+        <v>440</v>
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656783</t>
+          <t xml:space="preserve">311656782</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
@@ -31916,7 +31916,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 9B</t>
+          <t xml:space="preserve">Rådhusbuen 3</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
@@ -31931,15 +31931,15 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J426">
-        <v>440</v>
+        <v>5709</v>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656782</t>
+          <t xml:space="preserve">311657131</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
@@ -31949,7 +31949,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-30</t>
+          <t xml:space="preserve">2033-01-31</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -31991,7 +31991,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusbuen 3</t>
+          <t xml:space="preserve">Munkebro 2</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
@@ -32001,20 +32001,20 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">5303415</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J427">
-        <v>5709</v>
+        <v>608</v>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657131</t>
+          <t xml:space="preserve">311657447</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -32024,7 +32024,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-31</t>
+          <t xml:space="preserve">2033-02-01</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -32066,7 +32066,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munkebro 2</t>
+          <t xml:space="preserve">Sankt Ols Stræde 3</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
@@ -32081,15 +32081,15 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J428">
-        <v>608</v>
+        <v>858</v>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657447</t>
+          <t xml:space="preserve">311657449</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -32156,15 +32156,15 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J429">
-        <v>858</v>
+        <v>433</v>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657449</t>
+          <t xml:space="preserve">311657448</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
@@ -32216,7 +32216,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Ols Stræde 3</t>
+          <t xml:space="preserve">Absalonsgade 1</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -32226,7 +32226,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303415</t>
+          <t xml:space="preserve">8995768</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -32235,21 +32235,21 @@
         </is>
       </c>
       <c r="J430">
-        <v>433</v>
+        <v>378</v>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657448</t>
+          <t xml:space="preserve">311659172</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-01</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -32291,7 +32291,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absalonsgade 1</t>
+          <t xml:space="preserve">Absalonsgade 2</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -32306,11 +32306,11 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J431">
-        <v>378</v>
+        <v>6187</v>
       </c>
       <c r="K431" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absalonsgade 2</t>
+          <t xml:space="preserve">Rådhusbuen 1</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
@@ -32376,7 +32376,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995768</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -32385,21 +32385,21 @@
         </is>
       </c>
       <c r="J432">
-        <v>6187</v>
+        <v>9651</v>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659172</t>
+          <t xml:space="preserve">311666198</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspec ApS</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-02-14</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -32441,17 +32441,17 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusbuen 1</t>
+          <t xml:space="preserve">Baunegårdsvej 85</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">2177368</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -32460,21 +32460,21 @@
         </is>
       </c>
       <c r="J433">
-        <v>9651</v>
+        <v>3340</v>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666198</t>
+          <t xml:space="preserve">311664732</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-14</t>
+          <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -32531,11 +32531,11 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J434">
-        <v>3340</v>
+        <v>916</v>
       </c>
       <c r="K434" t="inlineStr">
         <is>
@@ -32606,11 +32606,11 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J435">
-        <v>916</v>
+        <v>900</v>
       </c>
       <c r="K435" t="inlineStr">
         <is>
@@ -32681,11 +32681,11 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J436">
-        <v>900</v>
+        <v>711</v>
       </c>
       <c r="K436" t="inlineStr">
         <is>
@@ -32756,11 +32756,11 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J437">
-        <v>711</v>
+        <v>1816</v>
       </c>
       <c r="K437" t="inlineStr">
         <is>
@@ -32816,30 +32816,30 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 85</t>
+          <t xml:space="preserve">Lynghøjen 107A</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177368</t>
+          <t xml:space="preserve">8995659</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J438">
-        <v>1816</v>
+        <v>817</v>
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664732</t>
+          <t xml:space="preserve">311665647</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
@@ -32849,7 +32849,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-07</t>
+          <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -32891,7 +32891,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107A</t>
+          <t xml:space="preserve">Lynghøjen 107B</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
@@ -32906,15 +32906,15 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J439">
-        <v>817</v>
+        <v>1552</v>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665647</t>
+          <t xml:space="preserve">311665669</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -32966,7 +32966,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107B</t>
+          <t xml:space="preserve">Lynghøjen 107C</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
@@ -32981,11 +32981,11 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J440">
-        <v>1552</v>
+        <v>433</v>
       </c>
       <c r="K440" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107C</t>
+          <t xml:space="preserve">Lynghøjen 107</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
@@ -33056,15 +33056,15 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J441">
-        <v>433</v>
+        <v>12308</v>
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665669</t>
+          <t xml:space="preserve">311666274</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
@@ -33074,7 +33074,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-10</t>
+          <t xml:space="preserve">2033-03-14</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -33116,7 +33116,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107</t>
+          <t xml:space="preserve">Industrileddet 4</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
@@ -33126,7 +33126,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995659</t>
+          <t xml:space="preserve">2180546</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -33135,21 +33135,21 @@
         </is>
       </c>
       <c r="J442">
-        <v>12308</v>
+        <v>2200</v>
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666274</t>
+          <t xml:space="preserve">311666541</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-14</t>
+          <t xml:space="preserve">2033-03-15</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -33191,7 +33191,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrileddet 4</t>
+          <t xml:space="preserve">Ollerupvej 5</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
@@ -33201,7 +33201,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180546</t>
+          <t xml:space="preserve">2173759</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -33210,21 +33210,21 @@
         </is>
       </c>
       <c r="J443">
-        <v>2200</v>
+        <v>12044</v>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666541</t>
+          <t xml:space="preserve">311667669</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-15</t>
+          <t xml:space="preserve">2033-03-20</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -33281,11 +33281,11 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J444">
-        <v>12044</v>
+        <v>494</v>
       </c>
       <c r="K444" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollerupvej 5</t>
+          <t xml:space="preserve">Ollerupvej 7</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
@@ -33356,15 +33356,15 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J445">
-        <v>494</v>
+        <v>826</v>
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667669</t>
+          <t xml:space="preserve">311667621</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollerupvej 7</t>
+          <t xml:space="preserve">Helligkorsvej 42A</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
@@ -33426,20 +33426,20 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173759</t>
+          <t xml:space="preserve">5312782</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J446">
-        <v>826</v>
+        <v>3137</v>
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667621</t>
+          <t xml:space="preserve">311670004</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
@@ -33449,7 +33449,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-20</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -33506,11 +33506,11 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J447">
-        <v>3137</v>
+        <v>6340</v>
       </c>
       <c r="K447" t="inlineStr">
         <is>
@@ -33581,11 +33581,11 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J448">
-        <v>6340</v>
+        <v>2165</v>
       </c>
       <c r="K448" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helligkorsvej 42A</t>
+          <t xml:space="preserve">Helligkorsvej 42C</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
@@ -33656,11 +33656,11 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J449">
-        <v>2165</v>
+        <v>778</v>
       </c>
       <c r="K449" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helligkorsvej 42C</t>
+          <t xml:space="preserve">Sønderlundsvej 58</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
@@ -33731,11 +33731,11 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J450">
-        <v>778</v>
+        <v>110</v>
       </c>
       <c r="K450" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderlundsvej 58</t>
+          <t xml:space="preserve">Ollerupvej 5C</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
@@ -33801,20 +33801,20 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312782</t>
+          <t xml:space="preserve">2173759</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J451">
-        <v>110</v>
+        <v>238</v>
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670004</t>
+          <t xml:space="preserve">311670514</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -33866,7 +33866,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollerupvej 5C</t>
+          <t xml:space="preserve">Østre Vindingevej 221A</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
@@ -33876,20 +33876,20 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173759</t>
+          <t xml:space="preserve">2209127</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J452">
-        <v>238</v>
+        <v>2177</v>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670514</t>
+          <t xml:space="preserve">311670922</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -33899,7 +33899,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -33956,11 +33956,11 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J453">
-        <v>2177</v>
+        <v>3318</v>
       </c>
       <c r="K453" t="inlineStr">
         <is>
@@ -34031,11 +34031,11 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J454">
-        <v>3318</v>
+        <v>766</v>
       </c>
       <c r="K454" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221A</t>
+          <t xml:space="preserve">Østre Vindingevej 221C</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
@@ -34106,15 +34106,15 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J455">
-        <v>766</v>
+        <v>2100</v>
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670922</t>
+          <t xml:space="preserve">311670926</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
@@ -34181,15 +34181,15 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J456">
-        <v>2100</v>
+        <v>201</v>
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670926</t>
+          <t xml:space="preserve">311670925</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -34241,7 +34241,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221C</t>
+          <t xml:space="preserve">Bistrup Bakke 5</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
@@ -34251,30 +34251,30 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209127</t>
+          <t xml:space="preserve">100513814</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">109</t>
         </is>
       </c>
       <c r="J457">
-        <v>201</v>
+        <v>1000</v>
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670925</t>
+          <t xml:space="preserve">311673245</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-31</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -34316,7 +34316,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 5</t>
+          <t xml:space="preserve">Bistrup Bakke 3</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
@@ -34331,15 +34331,15 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t xml:space="preserve">109</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J458">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673245</t>
+          <t xml:space="preserve">311675948</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
@@ -34349,7 +34349,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-04-24</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -34391,7 +34391,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 3</t>
+          <t xml:space="preserve">Bistrup Bakke 7</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
@@ -34406,15 +34406,15 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J459">
-        <v>997</v>
+        <v>1077</v>
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675948</t>
+          <t xml:space="preserve">311675950</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
@@ -34466,7 +34466,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 7</t>
+          <t xml:space="preserve">Astersvej 15</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
@@ -34476,30 +34476,30 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513814</t>
+          <t xml:space="preserve">8995869</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J460">
-        <v>1077</v>
+        <v>10347</v>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675950</t>
+          <t xml:space="preserve">311676003</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-24</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -34556,11 +34556,11 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J461">
-        <v>10347</v>
+        <v>6038</v>
       </c>
       <c r="K461" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 15</t>
+          <t xml:space="preserve">Astersvej 15C</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -34631,15 +34631,15 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J462">
-        <v>6038</v>
+        <v>643</v>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676003</t>
+          <t xml:space="preserve">311676217</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
@@ -34691,30 +34691,30 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 15C</t>
+          <t xml:space="preserve">Ørstedvej 63A</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995869</t>
+          <t xml:space="preserve">2217238</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J463">
-        <v>643</v>
+        <v>585</v>
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676217</t>
+          <t xml:space="preserve">311679099</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
@@ -34724,7 +34724,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-25</t>
+          <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -34766,30 +34766,30 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 63A</t>
+          <t xml:space="preserve">Kongebakken 19</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217238</t>
+          <t xml:space="preserve">9306000</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J464">
-        <v>585</v>
+        <v>6671</v>
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679099</t>
+          <t xml:space="preserve">311683094</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
@@ -34799,7 +34799,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-08</t>
+          <t xml:space="preserve">2033-05-25</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -34841,7 +34841,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongebakken 19</t>
+          <t xml:space="preserve">Kongebakken 19A</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
@@ -34851,7 +34851,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t xml:space="preserve">9306000</t>
+          <t xml:space="preserve">9306001</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -34860,11 +34860,11 @@
         </is>
       </c>
       <c r="J465">
-        <v>6671</v>
+        <v>630</v>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683094</t>
+          <t xml:space="preserve">311683580</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-25</t>
+          <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -34916,7 +34916,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongebakken 19A</t>
+          <t xml:space="preserve">Kongebakken 19B</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -34926,20 +34926,20 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t xml:space="preserve">9306001</t>
+          <t xml:space="preserve">9306000</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J466">
-        <v>630</v>
+        <v>245</v>
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683580</t>
+          <t xml:space="preserve">311683472</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
@@ -34991,7 +34991,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongebakken 19B</t>
+          <t xml:space="preserve">Trekroner Alle 1</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -35001,20 +35001,20 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">9306000</t>
+          <t xml:space="preserve">2174448</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J467">
-        <v>245</v>
+        <v>1216</v>
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683472</t>
+          <t xml:space="preserve">311725437</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -35024,7 +35024,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-26</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -35081,11 +35081,11 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J468">
-        <v>1216</v>
+        <v>1537</v>
       </c>
       <c r="K468" t="inlineStr">
         <is>
@@ -35156,11 +35156,11 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J469">
-        <v>1537</v>
+        <v>962</v>
       </c>
       <c r="K469" t="inlineStr">
         <is>
@@ -35231,11 +35231,11 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J470">
-        <v>962</v>
+        <v>3144</v>
       </c>
       <c r="K470" t="inlineStr">
         <is>
@@ -35306,11 +35306,11 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J471">
-        <v>3144</v>
+        <v>929</v>
       </c>
       <c r="K471" t="inlineStr">
         <is>
@@ -35381,11 +35381,11 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J472">
-        <v>929</v>
+        <v>553</v>
       </c>
       <c r="K472" t="inlineStr">
         <is>
@@ -35456,11 +35456,11 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J473">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="K473" t="inlineStr">
         <is>
@@ -35531,11 +35531,11 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J474">
-        <v>548</v>
+        <v>225</v>
       </c>
       <c r="K474" t="inlineStr">
         <is>
@@ -35606,15 +35606,15 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J475">
-        <v>225</v>
+        <v>599</v>
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725437</t>
+          <t xml:space="preserve">311725441</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
@@ -35681,15 +35681,15 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J476">
-        <v>599</v>
+        <v>224</v>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725441</t>
+          <t xml:space="preserve">311725437</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -35756,11 +35756,11 @@
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J477">
-        <v>224</v>
+        <v>715</v>
       </c>
       <c r="K477" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Alle 1</t>
+          <t xml:space="preserve">Trekroner Alle 1C</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
@@ -35831,15 +35831,15 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J478">
-        <v>715</v>
+        <v>2011</v>
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725437</t>
+          <t xml:space="preserve">311725438</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
@@ -35891,7 +35891,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Alle 1C</t>
+          <t xml:space="preserve">Piledyssen 50</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
@@ -35901,30 +35901,30 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174448</t>
+          <t xml:space="preserve">2172114</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J479">
-        <v>2011</v>
+        <v>595</v>
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725438</t>
+          <t xml:space="preserve">311743780</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør ApS</t>
         </is>
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2034-03-07</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -35966,7 +35966,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piledyssen 50</t>
+          <t xml:space="preserve">Vindeboder 7</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
@@ -35976,30 +35976,30 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172114</t>
+          <t xml:space="preserve">8934798</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J480">
-        <v>595</v>
+        <v>686</v>
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743780</t>
+          <t xml:space="preserve">311787742</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør ApS</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-07</t>
+          <t xml:space="preserve">2034-09-26</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -36056,11 +36056,11 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J481">
-        <v>686</v>
+        <v>452</v>
       </c>
       <c r="K481" t="inlineStr">
         <is>
@@ -36131,15 +36131,15 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J482">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787742</t>
+          <t xml:space="preserve">311787741</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -36206,15 +36206,15 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J483">
-        <v>479</v>
+        <v>310</v>
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787741</t>
+          <t xml:space="preserve">311787745</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
@@ -36266,7 +36266,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeboder 7</t>
+          <t xml:space="preserve">Østre Vindingevej 221A</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -36276,30 +36276,30 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t xml:space="preserve">8934798</t>
+          <t xml:space="preserve">2209127</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J484">
-        <v>310</v>
+        <v>470</v>
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787745</t>
+          <t xml:space="preserve">311793891</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
         </is>
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-26</t>
+          <t xml:space="preserve">2034-10-28</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -36341,7 +36341,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221A</t>
+          <t xml:space="preserve">Østre Vindingevej 219</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -36351,30 +36351,30 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209127</t>
+          <t xml:space="preserve">2209135</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J485">
-        <v>470</v>
+        <v>142</v>
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t xml:space="preserve">311793891</t>
+          <t xml:space="preserve">311824759</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiOptimo ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-28</t>
+          <t xml:space="preserve">2035-04-11</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -36416,7 +36416,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 219</t>
+          <t xml:space="preserve">Margrethevej 5</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209135</t>
+          <t xml:space="preserve">2171290</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -36435,21 +36435,21 @@
         </is>
       </c>
       <c r="J486">
-        <v>142</v>
+        <v>379</v>
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824759</t>
+          <t xml:space="preserve">311827298</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-11</t>
+          <t xml:space="preserve">2035-04-25</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -36491,7 +36491,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethevej 5</t>
+          <t xml:space="preserve">Kamstrupvej 1A</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -36501,7 +36501,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171290</t>
+          <t xml:space="preserve">2170150</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -36510,21 +36510,21 @@
         </is>
       </c>
       <c r="J487">
-        <v>379</v>
+        <v>1122</v>
       </c>
       <c r="K487" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827298</t>
+          <t xml:space="preserve">311827519</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-25</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -36566,7 +36566,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamstrupvej 1A</t>
+          <t xml:space="preserve">Margrethevej 3</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -36576,30 +36576,30 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170150</t>
+          <t xml:space="preserve">2171297</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J488">
-        <v>1122</v>
+        <v>243</v>
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827519</t>
+          <t xml:space="preserve">311833939</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2035-05-23</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -36641,7 +36641,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethevej 3</t>
+          <t xml:space="preserve">Store Valbyvej 248B</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
@@ -36651,20 +36651,20 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171297</t>
+          <t xml:space="preserve">2179764</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J489">
-        <v>243</v>
+        <v>6510</v>
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833939</t>
+          <t xml:space="preserve">311836213</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
@@ -36674,7 +36674,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-23</t>
+          <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -36716,7 +36716,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store Valbyvej 248B</t>
+          <t xml:space="preserve">Baunehøjvej 7</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
@@ -36726,7 +36726,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179764</t>
+          <t xml:space="preserve">2174627</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -36735,11 +36735,11 @@
         </is>
       </c>
       <c r="J490">
-        <v>6510</v>
+        <v>169</v>
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836213</t>
+          <t xml:space="preserve">311841999</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
@@ -36749,7 +36749,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-04</t>
+          <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -36806,15 +36806,15 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J491">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t xml:space="preserve">311841999</t>
+          <t xml:space="preserve">311842005</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
@@ -36881,15 +36881,15 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J492">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842005</t>
+          <t xml:space="preserve">311842009</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -36956,15 +36956,15 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J493">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842009</t>
+          <t xml:space="preserve">311842232</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
@@ -36974,7 +36974,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-01</t>
+          <t xml:space="preserve">2035-07-02</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -37016,7 +37016,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 7</t>
+          <t xml:space="preserve">Baunehøjvej 9</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
@@ -37031,15 +37031,15 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J494">
-        <v>165</v>
+        <v>410</v>
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842232</t>
+          <t xml:space="preserve">311842230</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -37091,7 +37091,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 9</t>
+          <t xml:space="preserve">Poppelgårdsvej 8</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -37101,30 +37101,30 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174627</t>
+          <t xml:space="preserve">100072983</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J495">
-        <v>410</v>
+        <v>280</v>
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842230</t>
+          <t xml:space="preserve">311846096</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-02</t>
+          <t xml:space="preserve">2035-07-24</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -37166,7 +37166,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelgårdsvej 8</t>
+          <t xml:space="preserve">Bredgade 17B</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
@@ -37176,7 +37176,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t xml:space="preserve">100072983</t>
+          <t xml:space="preserve">5303694</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -37185,11 +37185,11 @@
         </is>
       </c>
       <c r="J496">
-        <v>280</v>
+        <v>982</v>
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846096</t>
+          <t xml:space="preserve">311848390</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -37199,7 +37199,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-24</t>
+          <t xml:space="preserve">2035-08-11</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -37241,7 +37241,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 17B</t>
+          <t xml:space="preserve">Ringstedgade 16</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
@@ -37251,7 +37251,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303694</t>
+          <t xml:space="preserve">5303892</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -37260,11 +37260,11 @@
         </is>
       </c>
       <c r="J497">
-        <v>982</v>
+        <v>938</v>
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848390</t>
+          <t xml:space="preserve">311848394</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
@@ -37316,7 +37316,7 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedgade 16</t>
+          <t xml:space="preserve">Ringstedgade 22</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
@@ -37326,7 +37326,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303892</t>
+          <t xml:space="preserve">10239664</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -37335,11 +37335,11 @@
         </is>
       </c>
       <c r="J498">
-        <v>938</v>
+        <v>300</v>
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848394</t>
+          <t xml:space="preserve">311848392</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
@@ -37391,7 +37391,7 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedgade 22</t>
+          <t xml:space="preserve">Margrethevej 7</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t xml:space="preserve">10239664</t>
+          <t xml:space="preserve">2171297</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -37410,21 +37410,21 @@
         </is>
       </c>
       <c r="J499">
-        <v>300</v>
+        <v>8868</v>
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848392</t>
+          <t xml:space="preserve">311848839</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-11</t>
+          <t xml:space="preserve">2035-08-13</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -37466,7 +37466,7 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethevej 7</t>
+          <t xml:space="preserve">Urtevænget 10</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
@@ -37476,20 +37476,20 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171297</t>
+          <t xml:space="preserve">100513830</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="J500">
-        <v>8868</v>
+        <v>184</v>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848839</t>
+          <t xml:space="preserve">311856861</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -37499,7 +37499,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-13</t>
+          <t xml:space="preserve">2035-09-19</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -37541,7 +37541,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Urtevænget 10</t>
+          <t xml:space="preserve">Østre Kirkevej 7</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
@@ -37551,30 +37551,30 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513830</t>
+          <t xml:space="preserve">2173901</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J501">
-        <v>184</v>
+        <v>858</v>
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t xml:space="preserve">311856861</t>
+          <t xml:space="preserve">311871119</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-19</t>
+          <t xml:space="preserve">2035-11-27</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
@@ -37616,40 +37616,40 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Kirkevej 7</t>
+          <t xml:space="preserve">Ramsømaglevej 17C</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173901</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J502">
-        <v>858</v>
+        <v>1249</v>
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871119</t>
+          <t xml:space="preserve">311878552</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M502" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-27</t>
+          <t xml:space="preserve">2036-01-26</t>
         </is>
       </c>
       <c r="N502" t="inlineStr">
@@ -37691,40 +37691,40 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17C</t>
+          <t xml:space="preserve">Lises Markvej 2</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">100513466</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J503">
-        <v>1249</v>
+        <v>1387</v>
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878552</t>
+          <t xml:space="preserve">311890892</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M503" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-26</t>
+          <t xml:space="preserve">2036-03-27</t>
         </is>
       </c>
       <c r="N503" t="inlineStr">
@@ -37766,17 +37766,17 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lises Markvej 2</t>
+          <t xml:space="preserve">Hyldevænget 2</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513466</t>
+          <t xml:space="preserve">2213558</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -37785,21 +37785,21 @@
         </is>
       </c>
       <c r="J504">
-        <v>1387</v>
+        <v>530</v>
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t xml:space="preserve">311890892</t>
+          <t xml:space="preserve">311922906</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M504" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-27</t>
+          <t xml:space="preserve">2036-09-01</t>
         </is>
       </c>
       <c r="N504" t="inlineStr">
@@ -37841,7 +37841,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldevænget 2</t>
+          <t xml:space="preserve">Hyldevænget 4</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
@@ -37856,11 +37856,11 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J505">
-        <v>530</v>
+        <v>138</v>
       </c>
       <c r="K505" t="inlineStr">
         <is>
@@ -37916,30 +37916,30 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldevænget 4</t>
+          <t xml:space="preserve">Maglehøjen 6</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213558</t>
+          <t xml:space="preserve">5307587</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J506">
-        <v>138</v>
+        <v>1934</v>
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922906</t>
+          <t xml:space="preserve">311925372</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
@@ -37949,7 +37949,7 @@
       </c>
       <c r="M506" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-01</t>
+          <t xml:space="preserve">2036-09-11</t>
         </is>
       </c>
       <c r="N506" t="inlineStr">
@@ -37991,7 +37991,7 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglehøjen 6</t>
+          <t xml:space="preserve">Engbækvej 20</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
@@ -38001,30 +38001,30 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307587</t>
+          <t xml:space="preserve">9808161</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J507">
-        <v>1934</v>
+        <v>821</v>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925372</t>
+          <t xml:space="preserve">311928726</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M507" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-11</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N507" t="inlineStr">
@@ -38066,30 +38066,30 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbækvej 20</t>
+          <t xml:space="preserve">Agerskellet 13</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808161</t>
+          <t xml:space="preserve">7568845</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J508">
-        <v>821</v>
+        <v>354</v>
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928726</t>
+          <t xml:space="preserve">311931597</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -38099,7 +38099,7 @@
       </c>
       <c r="M508" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-29</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N508" t="inlineStr">
